--- a/sheets/국악이꽃피는나무/검수/삼다도 소식.xlsx
+++ b/sheets/국악이꽃피는나무/검수/삼다도 소식.xlsx
@@ -2809,20 +2809,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="57.14" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="63.76" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="63.76" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="63.76" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="63.76" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="63.76" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="63.76" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="63.76" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="63.76" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="63.76" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="63.76" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="63.76" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="63.76" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="63.76" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="63.76" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="63.76" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="63.76" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -3463,6 +3463,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
 </worksheet>
 </file>